--- a/dist/BSA-Onboarding-Trackers.xlsx
+++ b/dist/BSA-Onboarding-Trackers.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Each Monday sets a week plan around the 1:1-agreed top 3, blocks self-study, Anki and documentation time as in docs/05-time-management.md, and flags any slip to the Manager by Wednesday.</t>
+          <t>Each Friday drafts next week's plan (three outcomes, fixed commitments, booked reviews, 15% unplanned), agrees the top 3 in the 1:1, confirms it at the Monday confirm, blocks self-study, Anki and documentation time as in docs/05-time-management.md, and flags a slip to the Manager at the midpoint check, not at the deadline.</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Runs the owned tool end to end (before day 60: supervised in production or alone on a test copy; after the day-60 review: on schedule without help), recovers from its known failure modes, and is the named first point of contact in the Tool Inventory and OneNote.</t>
+          <t>Runs the owned tool end to end (before day 60: once, either supervised in production with the knowledge holder or alone on a test copy; after the day-60 review: on schedule without help), recovers from its known failure modes, is recorded as Knowledge holder today in the Tool Inventory, and is the owner and first point of contact in its tool doc in OneNote.</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Each Monday sets a week plan around the 1:1-agreed top 3, blocks self-study, Anki and documentation time as in docs/05-time-management.md, and flags any slip to the Manager by Wednesday.</t>
+          <t>Each Friday drafts next week's plan (three outcomes, fixed commitments, booked reviews, 15% unplanned), agrees the top 3 in the 1:1, confirms it at the Monday confirm, blocks self-study, Anki and documentation time as in docs/05-time-management.md, and flags a slip to the Manager at the midpoint check, not at the deadline.</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Runs the owned tool end to end (before day 60: supervised in production or alone on a test copy; after the day-60 review: on schedule without help), recovers from its known failure modes, and is the named first point of contact in the Tool Inventory and OneNote.</t>
+          <t>Runs the owned tool end to end (before day 60: once, either supervised in production with the knowledge holder or alone on a test copy; after the day-60 review: on schedule without help), recovers from its known failure modes, is recorded as Knowledge holder today in the Tool Inventory, and is the owner and first point of contact in its tool doc in OneNote.</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Planning a 40-hour week with 6-8 guided hours</t>
+          <t>Planning a 40-hour week with 5-8 guided hours</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -12442,12 +12442,12 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Draft the as-is doc for Research or Standard Cost from the template during the holiday weeks.</t>
+          <t>Draft the as-is doc for Research or Standard Cost from the template during the holiday weeks (solo drafting; the Manager reviews the draft in W10).</t>
         </is>
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Self-study</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
@@ -12500,12 +12500,12 @@
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Map own-process source fields to e2open concepts, profile the data, and log data-quality issues and cleansing candidates.</t>
+          <t>Map own-process source fields to e2open concepts, profile the data, and log data-quality issues and cleansing candidates (solo drafting; the Manager and the Senior review the draft in W11).</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Self-study</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Planning a 40-hour week with 6-8 guided hours</t>
+          <t>Planning a 40-hour week with 5-8 guided hours</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Draft the as-is doc for Research or Standard Cost from the template during the holiday weeks.</t>
+          <t>Draft the as-is doc for Research or Standard Cost from the template during the holiday weeks (solo drafting; the Manager reviews the draft in W10).</t>
         </is>
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Self-study</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Map own-process source fields to e2open concepts, profile the data, and log data-quality issues and cleansing candidates.</t>
+          <t>Map own-process source fields to e2open concepts, profile the data, and log data-quality issues and cleansing candidates (solo drafting; the Manager and the Senior review the draft in W11).</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Self-study</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>Drawback when imported goods, or substitutes classified in the same 8-digit HTS subheading, are exported or destroyed without being used in the US (19 U.S.C. 1313(j)). For substitution, an 8-digit line that begins 'Other' requires a 10-digit match.</t>
+          <t>Drawback when imported goods, or substitutes classified in the same 8-digit HTS subheading, are exported or destroyed without being used in the US (19 U.S.C. 1313(j)). For substitution, an 8-digit line that begins 'Other' requires a 10-digit match; if the 10-digit line also begins 'Other', substitution is not available (direct identification still is).</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
